--- a/forms/trg/Formulir_TRG_nutrifeed.xlsx
+++ b/forms/trg/Formulir_TRG_nutrifeed.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B41)</f>
+        <f>COUNTA(Anggota!B5:B42)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F41)</f>
+        <f>COUNTA(Anggota!F5:F42)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Djabal Nur Basir, S.Si., MSi</t>
+          <t>Prof.Dr.Ir. Sri Purwanti, S.Pt., M.Si., IPU., ASEAN.Eng</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,22 +928,18 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Materials and Analytical Measurement</t>
+          <t>Poultry Nutrition and Feed</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-0325-5669</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57217228332</t>
+          <t>56232605700</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Muh. Ridwan, M.Si., IPU</t>
+          <t>Dr. Djabal Nur Basir, S.Si., MSi</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,7 +969,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Livestock Industry Management</t>
+          <t>Materials and Analytical Measurement</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,13 +978,13 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2646-6987</t>
+          <t>0000-0003-0325-5669</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>59434928000</t>
+          <t>57217228332</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Wempie Pakiding, M.Sc</t>
+          <t>Dr. Ir. Muh. Ridwan, M.Si., IPU</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1018,7 +1014,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Poultry Livestock Production</t>
+          <t>Livestock Industry Management</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1027,13 +1023,13 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5650-8493</t>
+          <t>0000-0003-2646-6987</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>6602472294</t>
+          <t>59434928000</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,12 +1044,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Zaraswati Dwyana Zainuddin, M.Si</t>
+          <t>Dr. Ir. Wempie Pakiding, M.Sc</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1063,7 +1059,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Microbiology</t>
+          <t>Poultry Livestock Production</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1072,13 +1068,13 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5002-237X</t>
+          <t>0000-0001-5650-8493</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>58793481800</t>
+          <t>6602472294</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1093,12 +1089,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Gemini Alam, M.Si., Apt</t>
+          <t>Prof. Dr. Zaraswati Dwyana Zainuddin, M.Si</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1108,7 +1104,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Pharmacognosy and Phytochemistry</t>
+          <t>Microbiology</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1117,13 +1113,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-7721-9658</t>
+          <t>0000-0001-5002-237X</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>6507286881</t>
+          <t>58793481800</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1138,12 +1134,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Jasmal A. Syamsu, M.Si., IPU., ASEAN.Eng</t>
+          <t>Prof. Dr. Gemini Alam, M.Si., Apt</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1153,7 +1149,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Feed Science and Technology</t>
+          <t>Pharmacognosy and Phytochemistry</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1162,13 +1158,13 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-0795-5366</t>
+          <t>0000-0001-7721-9658</t>
         </is>
       </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57208472974</t>
+          <t>6507286881</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1183,12 +1179,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Asmuddin Natsir, M.Sc</t>
+          <t>Prof. Dr. Ir. Jasmal A. Syamsu, M.Si., IPU., ASEAN.Eng</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1198,7 +1194,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Animal Nutrition Science</t>
+          <t>Feed Science and Technology</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1207,13 +1203,13 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-4719-3519</t>
+          <t>0000-0002-0795-5366</t>
         </is>
       </c>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>8290761000</t>
+          <t>57208472974</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1228,22 +1224,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Anjas Asmara @ Ab. Hadi Bin Samsudin</t>
+          <t>Prof. Dr. Ir. Asmuddin Natsir, M.Sc</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Institute of Tropical Agriculture and Food Security (ITAFoS), Universiti Putra Malaysia (UPM)</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Animal Nutrition</t>
+          <t>Animal Nutrition Science</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1252,13 +1248,13 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-9758-7973</t>
+          <t>0000-0003-4719-3519</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>54401635800</t>
+          <t>8290761000</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1273,22 +1269,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ahmad Sofyan, S.Pt., M.Sc., Ph.D</t>
+          <t>Prof. Dr. Anjas Asmara @ Ab. Hadi Bin Samsudin</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency (Badan Riset dan Inovasi Nasional-BRIN), Indonesia</t>
+          <t>Institute of Tropical Agriculture and Food Security (ITAFoS), Universiti Putra Malaysia (UPM)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Feed additive</t>
+          <t>Animal Nutrition</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1297,13 +1293,13 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-0578-4671</t>
+          <t>0000-0002-9758-7973</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>57136745300</t>
+          <t>54401635800</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1318,31 +1314,39 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Ir. Teddy Candinegara</t>
+          <t>Prof. Ahmad Sofyan, S.Pt., M.Sc., Ph.D</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Behn Meyer Chemicals, Indonesia</t>
+          <t>National Research and Innovation Agency (Badan Riset dan Inovasi Nasional-BRIN), Indonesia</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Feed Additive</t>
+          <t>Feed additive</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-0578-4671</t>
+        </is>
+      </c>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>57136745300</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1355,18 +1359,22 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Ir. Alfred Kompudu, S.Pt., MM., IPM., ASEAN Eng.</t>
+          <t>Ir. Teddy Candinegara</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Behn Meyer Chemicals, Indonesia</t>
+        </is>
+      </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>U.S. Soybean Export Council-Animal Protein Technical Counsultant– Indonesia</t>
+          <t>Feed Additive</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1388,39 +1396,27 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Umair Asghar</t>
+          <t>Ir. Alfred Kompudu, S.Pt., MM., IPM., ASEAN Eng.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>University of Environmental and Life Sciences (UPWr), Poland</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n"/>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Animal Nutrition</t>
+          <t>U.S. Soybean Export Council-Animal Protein Technical Counsultant– Indonesia</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-2838-0749</t>
-        </is>
-      </c>
+      <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>https://www.scopus.com/pages/authors/56954467000</t>
-        </is>
-      </c>
+      <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1433,22 +1429,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Andi Muh Fuad Al Kautsar Walinono, S.Pt., M.Si</t>
+          <t>Dr. Muhammad Umair Asghar</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>University of Environmental and Life Sciences (UPWr), Poland</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Animal Feed</t>
+          <t>Animal Nutrition</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1457,11 +1453,15 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>0009-0009-9074-5578</t>
+          <t>0000-0003-2838-0749</t>
         </is>
       </c>
       <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/authors/56954467000</t>
+        </is>
+      </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Ichlasul Amal, S.Pt., M.Si.</t>
+          <t>Andi Muh Fuad Al Kautsar Walinono, S.Pt., M.Si</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1498,15 +1498,11 @@
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-3120-7269</t>
+          <t>0009-0009-9074-5578</t>
         </is>
       </c>
       <c r="K18" s="12" t="n"/>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>57225936343</t>
-        </is>
-      </c>
+      <c r="L18" s="12" t="n"/>
       <c r="M18" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1519,12 +1515,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Lisa Nashfati Muhammad, S.Pt., M.Si</t>
+          <t>Ichlasul Amal, S.Pt., M.Si.</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1534,16 +1530,24 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Poultry Nutrition and Feed</t>
+          <t>Animal Feed</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
-      <c r="J19" s="12" t="n"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-3120-7269</t>
+        </is>
+      </c>
       <c r="K19" s="12" t="n"/>
-      <c r="L19" s="12" t="n"/>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>57225936343</t>
+        </is>
+      </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1556,12 +1560,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>drh. Adyatma Muhammad Nur, M.Si.</t>
+          <t>Lisa Nashfati Muhammad, S.Pt., M.Si</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1571,7 +1575,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Public Health</t>
+          <t>Poultry Nutrition and Feed</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1593,39 +1597,31 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Khaerani Kiramang</t>
+          <t>drh. Adyatma Muhammad Nur, M.Si.</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Universitas Islam Negeri Makassar</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Doctoral student</t>
+          <t>Veterinary Public Health</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-3489-3209</t>
-        </is>
-      </c>
+      <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>57208470639</t>
-        </is>
-      </c>
+      <c r="L21" s="12" t="n"/>
       <c r="M21" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1638,31 +1634,39 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Santi</t>
+          <t>Khaerani Kiramang</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Universitas Al Asyariah Mandar</t>
+          <t>Universitas Islam Negeri Makassar</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Doctoral Student</t>
+          <t>Doctoral student</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="12" t="n"/>
       <c r="H22" s="12" t="n"/>
       <c r="I22" s="12" t="n"/>
-      <c r="J22" s="12" t="n"/>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-3489-3209</t>
+        </is>
+      </c>
       <c r="K22" s="12" t="n"/>
-      <c r="L22" s="12" t="n"/>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>57208470639</t>
+        </is>
+      </c>
       <c r="M22" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1675,22 +1679,22 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Khaerunnisa</t>
+          <t>Santi</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universitas Al Asyariah Mandar</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Magister Student</t>
+          <t>Doctoral Student</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -1712,12 +1716,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Musmalika</t>
+          <t>Khaerunnisa</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1749,12 +1753,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Mita Lestari</t>
+          <t>Musmalika</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1786,12 +1790,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Andi Isneni</t>
+          <t>Mita Lestari</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -1801,7 +1805,7 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Magister student</t>
+          <t>Magister Student</t>
         </is>
       </c>
       <c r="F26" s="12" t="n"/>
@@ -1823,12 +1827,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Alfian Salama Samsul</t>
+          <t>Andi Isneni</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -1860,12 +1864,12 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Armayani M</t>
+          <t>Alfian Salama Samsul</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -1875,7 +1879,7 @@
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Doctoral Student</t>
+          <t>Magister student</t>
         </is>
       </c>
       <c r="F28" s="12" t="n"/>
@@ -1897,22 +1901,22 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Sri Rahmani Inayah</t>
+          <t>Armayani M</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
           <t>Doctoral Student</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>PouNutriFeed Team</t>
         </is>
       </c>
       <c r="F29" s="12" t="n"/>
@@ -1921,11 +1925,7 @@
       <c r="I29" s="12" t="n"/>
       <c r="J29" s="12" t="n"/>
       <c r="K29" s="12" t="n"/>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>58002032800</t>
-        </is>
-      </c>
+      <c r="L29" s="12" t="n"/>
       <c r="M29" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1936,18 +1936,42 @@
       <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="11" t="n"/>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Sri Rahmani Inayah</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Doctoral Student</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>PouNutriFeed Team</t>
+        </is>
+      </c>
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="12" t="n"/>
       <c r="H30" s="12" t="n"/>
       <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
       <c r="K30" s="12" t="n"/>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>58002032800</t>
+        </is>
+      </c>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2136,15 +2160,32 @@
       <c r="L41" s="12" t="n"/>
       <c r="M41" s="12" t="n"/>
     </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="12" t="n"/>
+      <c r="M42" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
